--- a/kawasaki_project/05_試算・管理シート/川崎町_第10期_施策事業統合体系表_R8.9.25b.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_第10期_施策事業統合体系表_R8.9.25b.xlsx
@@ -3662,7 +3662,7 @@
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>退院前カンファレンス・ACP（人生会議）の普及。町外医療機関との広域連携（第1章第1節2(3)）と一体で運用する。体制は整っているが活動量が伴っていないため、ACPと入退院支援の実施件数を第10期の重点とする</t>
+          <t>退院前カンファレンス・ACP（人生会議）の普及。町外医療機関との広域連携（第1章第1節2(3)）と一体で運用する。体制は整っているが活動量が伴っていないため、ACPと入退院支援の実施件数を第10期の重点とする。人生の最終段階における支援は3年連続0点であり、同規模かつ過疎地域の285保険者の平均3.6点も全国平均6.4点を下回る。まず実施の記録を残す運用から始める（素案3-3）</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>配置数は県内1位だが会議への参加が0点。自立支援型地域ケア会議（第2節1(5)）への出席を運用で確保すれば得点できる</t>
+          <t>配置数は県内1位だが会議への参加が3年連続0点。自立支援型地域ケア会議（第2節1(5)）への出席を運用で確保すれば得点できる。同規模かつ過疎地域の285保険者のうち161件（56.5％）が満点を取っており、0点9指標のなかで最も取りやすい（素案3-3）</t>
         </is>
       </c>
     </row>
@@ -3897,41 +3897,49 @@
       <c r="I77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>第４章 地域支援事業の充実</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>第２節 包括的支援事業・任意事業</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>３　任意事業</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>（１）介護給付費等適正化事業</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr"/>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>拡充</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>交：「給付費適正化方策の策定状況」は3年連続32点満点・県内1位である一方、「給付費適正化事業の取組状況」は令和7年度36点から令和8年度30／36点に低下。「医療情報との突合」は16点満点・県内1位</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>保健福祉課</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr"/>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>第7章2（介護費用適正化の推進）と一体で運用する</t>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>給付費適正化事業の取組項目数</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>柱7 2（介護費用適正化の推進）と一体で運用する。令和8年度に落ちた項目を確認中【町確認】</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4424,7 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月25日の交付金データの再解析で判明。町の事業一覧・計画素案のいずれにも記載がなかった。難聴は認知症の危険因子として国際的に確立しており、全国平均の約3倍の評価を得ている本町の強みである。事業内容（実施方法・対象・件数）を確認中【町確認】</t>
+          <t>令和8年9月25日の交付金データの再解析で判明。町の事業一覧・計画素案のいずれにも記載がなかった。難聴は認知症の危険因子として国際的に確立しており、全国平均の約3倍の評価を得ている本町の強みである。令和7年度に指標が新設された初年度から2年連続で満点であり（全国平均は令和7年度4.5点・令和8年度6.9点）、制度ができる前から町が取り組んでいたことを示している。事業内容（実施方法・対象・件数）を確認中【町確認】</t>
         </is>
       </c>
     </row>
@@ -6427,39 +6435,51 @@
       <c r="I139" s="5" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
+      <c r="A140" s="7" t="inlineStr">
         <is>
           <t>第７章 地域マネジメントに関する事項</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B140" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C140" s="5" t="inlineStr">
+      <c r="C140" s="7" t="inlineStr">
         <is>
           <t>１　介護サービスの質の向上</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
-        <is>
-          <t>（１）研修・指導・苦情対応</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
-        </is>
-      </c>
-      <c r="F140" s="5" t="inlineStr"/>
-      <c r="G140" s="5" t="inlineStr">
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>（１）研修・指導・苦情対応・ケアプラン点検</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>拡充</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>交：「ケアプラン点検の実施状況」は令和6年度8点から令和7・8年度は4／16点に下がり、全国平均6.4点を下回る（県内13位）</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
         <is>
           <t>保健福祉課</t>
         </is>
       </c>
-      <c r="H140" s="5" t="inlineStr"/>
-      <c r="I140" s="5" t="inlineStr"/>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>ケアプラン点検の実施件数</t>
+        </is>
+      </c>
+      <c r="I140" s="7" t="inlineStr">
+        <is>
+          <t>素案は複数箇所でケアプラン点検を施策として掲げているが、交付金評価では令和7年度から全国平均を下回っている。点検件数と実施方法を確認中【町確認】</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -6613,7 +6633,7 @@
       </c>
       <c r="I144" s="7" t="inlineStr">
         <is>
-          <t>第2回策定委員会 選択4。町単独事業は地域支援事業の対象外であり第1号保険料では賄えない。体制は県内1位だが研修の実施が2項目とも0点であり、研修の実施が最も手当てしやすい失点である（計24点）</t>
+          <t>第2回策定委員会 選択4。町単独事業は地域支援事業の対象外であり第1号保険料では賄えない。体制は県内1位だが研修の実施が3年連続で2項目とも0点（計24点）。ただし同規模かつ過疎地域の285保険者でも満点は15件・9件（3〜5％）にとどまり、取れなくても同規模団体との比較では不利にならない。第2回策定委員会の選択4のご判断による（素案3-3）</t>
         </is>
       </c>
     </row>
@@ -6975,10 +6995,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7068,10 +7088,10 @@
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -7099,10 +7119,10 @@
         <v>143</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -7125,7 +7145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7617,7 +7637,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>退院前カンファレンス・ACP（人生会議）の普及。町外医療機関との広域連携（第1章第1節2(3)）と一体で運用する。体制は整っているが活動量が伴っていないため、ACPと入退院支援の実施件数を第10期の重点とする</t>
+          <t>退院前カンファレンス・ACP（人生会議）の普及。町外医療機関との広域連携（第1章第1節2(3)）と一体で運用する。体制は整っているが活動量が伴っていないため、ACPと入退院支援の実施件数を第10期の重点とする。人生の最終段階における支援は3年連続0点であり、同規模かつ過疎地域の285保険者の平均3.6点も全国平均6.4点を下回る。まず実施の記録を残す運用から始める（素案3-3）</t>
         </is>
       </c>
     </row>
@@ -7671,34 +7691,34 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>配置数は県内1位だが会議への参加が0点。自立支援型地域ケア会議（第2節1(5)）への出席を運用で確保すれば得点できる</t>
+          <t>配置数は県内1位だが会議への参加が3年連続0点。自立支援型地域ケア会議（第2節1(5)）への出席を運用で確保すれば得点できる。同規模かつ過疎地域の285保険者のうち161件（56.5％）が満点を取っており、0点9指標のなかで最も取りやすい（素案3-3）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>拡充</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>第５章 認知症施策の推進</t>
+          <t>第４章 地域支援事業の充実</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>（１）認知症の人及びその家族等からの意見聴取</t>
+          <t>（１）介護給付費等適正化事業</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>法：第13条第3項において準用する第12条第3項</t>
+          <t>交：「給付費適正化方策の策定状況」は3年連続32点満点・県内1位である一方、「給付費適正化事業の取組状況」は令和7年度36点から令和8年度30／36点に低下。「医療情報との突合」は16点満点・県内1位</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>計画書案の作成前に実施する。対象者の選定（認知症カフェの参加者・初期集中支援チームの対象者等）は町と協議のうえ決定する（確認事項No.90）</t>
+          <t>柱7 2（介護費用適正化の推進）と一体で運用する。令和8年度に落ちた項目を確認中【町確認】</t>
         </is>
       </c>
     </row>
@@ -7715,17 +7735,17 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>（２）計画の公表</t>
+          <t>（１）認知症の人及びその家族等からの意見聴取</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>法：第13条第3項において準用する第12条第4項</t>
+          <t>法：第13条第3項において準用する第12条第3項</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>第9期計画では行っていなかった</t>
+          <t>計画書案の作成前に実施する。対象者の選定（認知症カフェの参加者・初期集中支援チームの対象者等）は町と協議のうえ決定する（確認事項No.90）</t>
         </is>
       </c>
     </row>
@@ -7742,17 +7762,17 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>（３）実施状況の評価と結果の公表</t>
+          <t>（２）計画の公表</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>法：第13条第3項において準用する第12条第5項・第6項</t>
+          <t>法：第13条第3項において準用する第12条第4項</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>交付金の評価指標「進捗状況の評価に当たり認知症の当事者の意見を聴いているか」と同内容（確認事項No.93）</t>
+          <t>第9期計画では行っていなかった</t>
         </is>
       </c>
     </row>
@@ -7769,15 +7789,19 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>（４）少なくとも5年ごとの検討</t>
+          <t>（３）実施状況の評価と結果の公表</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>法：第13条第3項において準用する第12条第7項</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr"/>
+          <t>法：第13条第3項において準用する第12条第5項・第6項</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>交付金の評価指標「進捗状況の評価に当たり認知症の当事者の意見を聴いているか」と同内容（確認事項No.93）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -7792,24 +7816,20 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>（５）他の計画との調和</t>
+          <t>（４）少なくとも5年ごとの検討</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>法：第13条第2項（地域福祉計画・老人福祉計画・介護保険事業計画等）</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>本計画を一体の計画として策定することにより調和を確保する</t>
-        </is>
-      </c>
+          <t>法：第13条第3項において準用する第12条第7項</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>拡充</t>
+          <t>新規</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
@@ -7819,17 +7839,17 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>（１）認知症初期集中支援推進事業【重点】</t>
+          <t>（５）他の計画との調和</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>実：訪問件数が令和5年度80件→令和6年度42件→令和7年度見込12件と2年で85％減</t>
+          <t>法：第13条第2項（地域福祉計画・老人福祉計画・介護保険事業計画等）</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>法第21条第2項の連携協力体制の整備に当たる。活動量の回復を図る場合は目標値を別に定める（確認事項No.89・No.96）</t>
+          <t>本計画を一体の計画として策定することにより調和を確保する</t>
         </is>
       </c>
     </row>
@@ -7846,17 +7866,17 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>（１）認知症サポーター養成講座の開催</t>
+          <t>（１）認知症初期集中支援推進事業【重点】</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>交：「認知症サポーター数」0／12点・県内22位。令和7年3月31日時点577人。高齢者人口10万人当たり17,694人で全国1,592位</t>
+          <t>実：訪問件数が令和5年度80件→令和6年度42件→令和7年度見込12件と2年で85％減</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>町提供データの累計642人との食い違いを確認中（確認事項No.94）</t>
+          <t>法第21条第2項の連携協力体制の整備に当たる。活動量の回復を図る場合は目標値を別に定める（確認事項No.89・No.96）</t>
         </is>
       </c>
     </row>
@@ -7873,17 +7893,17 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>（３）チームオレンジの整備・活動支援</t>
+          <t>（１）認知症サポーター養成講座の開催</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>交：ステップアップ講座修了者828人で全国188位（全国平均330人）</t>
+          <t>交：「認知症サポーター数」0／12点・県内22位。令和7年3月31日時点577人。高齢者人口10万人当たり17,694人で全国1,592位</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>令和6年度に整備済み。第10期は活動の充実とチーム数の拡大。本町の強みは人数ではなく担い手の層（確認事項No.87）</t>
+          <t>町提供データの累計642人との食い違いを確認中（確認事項No.94）</t>
         </is>
       </c>
     </row>
@@ -7900,20 +7920,24 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>（４）企業・学校等における認知症サポーターの養成</t>
+          <t>（３）チームオレンジの整備・活動支援</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>法：認知症基本法第14条（学校教育・社会教育における認知症教育の推進）</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr"/>
+          <t>交：ステップアップ講座修了者828人で全国188位（全国平均330人）</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>令和6年度に整備済み。第10期は活動の充実とチーム数の拡大。本町の強みは人数ではなく担い手の層（確認事項No.87）</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>拡充</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -7923,19 +7947,15 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>（１）認知症本人ミーティングの開催</t>
+          <t>（４）企業・学校等における認知症サポーターの養成</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>法：認知症基本法第16条第1項（経験等を共有できる機会・社会参加の機会の確保）</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>体系（案）に対応する事業がなかった（確認事項No.112）</t>
-        </is>
-      </c>
+          <t>法：認知症基本法第14条（学校教育・社会教育における認知症教育の推進）</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -7950,17 +7970,17 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>（２）若年性認知症の人の就労継続に関する事業主への啓発</t>
+          <t>（１）認知症本人ミーティングの開催</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>法：認知症基本法第16条第2項（雇用の継続・円滑な就職）</t>
+          <t>法：認知症基本法第16条第1項（経験等を共有できる機会・社会参加の機会の確保）</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>町における該当者の把握状況とあわせて確認中（確認事項No.95）</t>
+          <t>体系（案）に対応する事業がなかった（確認事項No.112）</t>
         </is>
       </c>
     </row>
@@ -7977,15 +7997,19 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>（２）日常生活自立支援事業の活用</t>
+          <t>（２）若年性認知症の人の就労継続に関する事業主への啓発</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>法：認知症基本法第17条</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr"/>
+          <t>法：認知症基本法第16条第2項（雇用の継続・円滑な就職）</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>町における該当者の把握状況とあわせて確認中（確認事項No.95）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -8000,12 +8024,12 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>（３）意思決定支援研修の実施</t>
+          <t>（２）日常生活自立支援事業の活用</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>法：認知症基本法第17条（意思決定支援に関する指針）</t>
+          <t>法：認知症基本法第17条</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr"/>
@@ -8023,19 +8047,15 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>（１）国の研究成果の活用と普及</t>
+          <t>（３）意思決定支援研修の実施</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>法：認知症基本法第20条</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>体系（案）に対応する事業がなかった（確認事項No.112）</t>
-        </is>
-      </c>
+          <t>法：認知症基本法第17条（意思決定支援に関する指針）</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -8050,17 +8070,17 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>（２）意見聴取の結果の施策への反映</t>
+          <t>（１）国の研究成果の活用と普及</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>法：認知症基本法第20条（社会参加の在り方等の調査研究と成果の活用）</t>
+          <t>法：認知症基本法第20条</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>第1節1(1)の意見聴取と一体で運用する</t>
+          <t>体系（案）に対応する事業がなかった（確認事項No.112）</t>
         </is>
       </c>
     </row>
@@ -8077,17 +8097,17 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>（１）認知症の日（9月21日）にふさわしい事業の実施</t>
+          <t>（２）意見聴取の結果の施策への反映</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>法：認知症基本法第9条第2項</t>
+          <t>法：認知症基本法第20条（社会参加の在り方等の調査研究と成果の活用）</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>本町には現在これに当たる取組がない。認知症カフェ・サポーター養成講座を9月に集中させる等、既存の事業で対応できる余地がある（確認事項No.92）</t>
+          <t>第1節1(1)の意見聴取と一体で運用する</t>
         </is>
       </c>
     </row>
@@ -8104,44 +8124,44 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>（２）認知症月間（9月1日〜30日）の行事の奨励</t>
+          <t>（１）認知症の日（9月21日）にふさわしい事業の実施</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>法：認知症基本法第9条第3項</t>
+          <t>法：認知症基本法第9条第2項</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>素案Ver.1.18までは「世界アルツハイマー月間」としていたが、これは国際的な呼称であり法定の認知症の日・認知症月間とは別のもの</t>
+          <t>本町には現在これに当たる取組がない。認知症カフェ・サポーター養成講座を9月に集中させる等、既存の事業で対応できる余地がある（確認事項No.92）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>拡充</t>
+          <t>新規</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>第７章 地域マネジメントに関する事項</t>
+          <t>第５章 認知症施策の推進</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>（１）介護人材の確保・育成</t>
+          <t>（２）認知症月間（9月1日〜30日）の行事の奨励</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>交：推進 目標Ⅲ「確保・定着の取組状況」30点満点・「庁内庁外の連携体制」34点満点でいずれも県内1位である一方、「介護の仕事の魅力に関する研修」0／12点・「定着・資質向上に関する研修」0／12点。委：1ユニット分の人員削減、職員80名→50名の見込み、人材紹介に1件約100万円の紹介料</t>
+          <t>法：認知症基本法第9条第3項</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>第2回策定委員会 選択4。町単独事業は地域支援事業の対象外であり第1号保険料では賄えない。体制は県内1位だが研修の実施が2項目とも0点であり、研修の実施が最も手当てしやすい失点である（計24点）</t>
+          <t>素案Ver.1.18までは「世界アルツハイマー月間」としていたが、これは国際的な呼称であり法定の認知症の日・認知症月間とは別のもの</t>
         </is>
       </c>
     </row>
@@ -8158,24 +8178,24 @@
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>（１）目標と指標の設定・管理</t>
+          <t>（１）研修・指導・苦情対応・ケアプラン点検</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>交：第9期のアウトカム指標は調整済み認定率を令和5年の水準（17.6％）に維持すること</t>
+          <t>交：「ケアプラン点検の実施状況」は令和6年度8点から令和7・8年度は4／16点に下がり、全国平均6.4点を下回る（県内13位）</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>各指標に指標名・区分・現状値・目標値・集計担当・集計方法及び頻度・未把握の場合の対応を必ず付す</t>
+          <t>素案は複数箇所でケアプラン点検を施策として掲げているが、交付金評価では令和7年度から全国平均を下回っている。点検件数と実施方法を確認中【町確認】</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>拡充</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -8185,42 +8205,96 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>（１）乖離の把握と公表</t>
+          <t>（１）介護人材の確保・育成</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>交：令和8年度の保険者機能強化推進交付金で「評価結果の活用」が令和7年度の満点16点から0点。県内35保険者中34位</t>
+          <t>交：推進 目標Ⅲ「確保・定着の取組状況」30点満点・「庁内庁外の連携体制」34点満点でいずれも県内1位である一方、「介護の仕事の魅力に関する研修」0／12点・「定着・資質向上に関する研修」0／12点。委：1ユニット分の人員削減、職員80名→50名の見込み、人材紹介に1件約100万円の紹介料</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>体系（案）にない施策。7に含めるか8として立てるかを確認中（確認事項No.108）</t>
+          <t>第2回策定委員会 選択4。町単独事業は地域支援事業の対象外であり第1号保険料では賄えない。体制は県内1位だが研修の実施が3年連続で2項目とも0点（計24点）。ただし同規模かつ過疎地域の285保険者でも満点は15件・9件（3〜5％）にとどまり、取れなくても同規模団体との比較では不利にならない。第2回策定委員会の選択4のご判断による（素案3-3）</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
+          <t>拡充</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>第７章 地域マネジメントに関する事項</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>（１）目標と指標の設定・管理</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>交：第9期のアウトカム指標は調整済み認定率を令和5年の水準（17.6％）に維持すること</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>各指標に指標名・区分・現状値・目標値・集計担当・集計方法及び頻度・未把握の場合の対応を必ず付す</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
           <t>新規</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>第７章 地域マネジメントに関する事項</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>（１）乖離の把握と公表</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>交：令和8年度の保険者機能強化推進交付金で「評価結果の活用」が令和7年度の満点16点から0点。県内35保険者中34位</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>体系（案）にない施策。7に含めるか8として立てるかを確認中（確認事項No.108）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>第７章 地域マネジメントに関する事項</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>（１）住所地特例該当者の把握</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>実：住所地特例該当者24人（令和7年6月時点）</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>体系（案）にない施策。町外施設（柴田町・大河原町・仙台市等）への依存が常態化しており、所在自治体内訳の把握を見込量算定と広域連携の根拠とする</t>
         </is>

--- a/kawasaki_project/05_試算・管理シート/川崎町_第10期_施策事業統合体系表_R8.9.25b.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_第10期_施策事業統合体系表_R8.9.25b.xlsx
@@ -525,7 +525,6 @@
       <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" s="2" t="n"/>
     </row>
     <row r="4">
@@ -553,7 +552,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>計画書素案 Ver.1.20（令和8年9月17日）</t>
@@ -561,7 +559,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>令和8年6〜7月実施の2調査（一般高齢者576件・認定者142件）</t>
@@ -569,7 +566,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価結果</t>
@@ -577,7 +573,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）</t>
@@ -585,7 +580,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" s="2" t="n"/>
     </row>
     <row r="11">
@@ -601,7 +595,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" s="2" t="n"/>
     </row>
     <row r="13">
@@ -673,7 +666,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" s="2" t="n"/>
     </row>
     <row r="20">
@@ -745,7 +737,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" s="2" t="n"/>
     </row>
     <row r="27">
@@ -757,7 +748,6 @@
       <c r="B27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>所管に【町確認】を付した事業は、担当課の確定をお願いします。</t>
@@ -765,7 +755,6 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>KPI候補は重点事業に限って置いています。全事業に置くかは確認事項No.109でご判断ください。</t>
@@ -773,7 +762,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>第9期の事業別実績（実施回数・対象者数・決算額）の記入を経て現状値を確定します（資料提供依頼No.34）。</t>
@@ -6214,7 +6202,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>（７）地域密着型介護老人福祉施設入居者生活介護（小規模特別養護老人ホーム）</t>
+          <t>（７）地域密着型介護老人福祉施設入所者生活介護（小規模特別養護老人ホーム）</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_第10期_施策事業統合体系表_R8.9.25b.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_第10期_施策事業統合体系表_R8.9.25b.xlsx
@@ -525,6 +525,7 @@
       <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" s="2" t="n"/>
     </row>
     <row r="4">
@@ -552,6 +553,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>計画書素案 Ver.1.20（令和8年9月17日）</t>
@@ -559,6 +561,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>令和8年6〜7月実施の2調査（一般高齢者576件・認定者142件）</t>
@@ -566,6 +569,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価結果</t>
@@ -573,6 +577,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>共生社会の実現を推進するための認知症基本法（令和5年法律第65号）</t>
@@ -580,6 +585,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" s="2" t="n"/>
     </row>
     <row r="11">
@@ -595,6 +601,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" s="2" t="n"/>
     </row>
     <row r="13">
@@ -666,6 +673,7 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr"/>
       <c r="B19" s="2" t="n"/>
     </row>
     <row r="20">
@@ -737,6 +745,7 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr"/>
       <c r="B26" s="2" t="n"/>
     </row>
     <row r="27">
@@ -748,6 +757,7 @@
       <c r="B27" s="2" t="n"/>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>所管に【町確認】を付した事業は、担当課の確定をお願いします。</t>
@@ -755,6 +765,7 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>KPI候補は重点事業に限って置いています。全事業に置くかは確認事項No.109でご判断ください。</t>
@@ -762,6 +773,7 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>第9期の事業別実績（実施回数・対象者数・決算額）の記入を経て現状値を確定します（資料提供依頼No.34）。</t>
@@ -3728,7 +3740,7 @@
       <c r="H73" s="9" t="inlineStr"/>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>体系（案）にない施策。8050問題・ヤングケアラー・ダブルケア等の複合的な課題を抱える世帯への包括的支援。地域福祉計画・障害者計画はジャパン総研が策定担当</t>
+          <t>体系（案）にない施策。8050問題・ヤングケアラー・ダブルケア等の複合的な課題を抱える世帯への包括的支援。地域福祉計画・障害者計画は別途策定</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7664,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>体系（案）にない施策。8050問題・ヤングケアラー・ダブルケア等の複合的な課題を抱える世帯への包括的支援。地域福祉計画・障害者計画はジャパン総研が策定担当</t>
+          <t>体系（案）にない施策。8050問題・ヤングケアラー・ダブルケア等の複合的な課題を抱える世帯への包括的支援。地域福祉計画・障害者計画は別途策定</t>
         </is>
       </c>
     </row>
